--- a/data-preprocessing/rpc-footprints/1 - Crops/Mushrooms.xlsx
+++ b/data-preprocessing/rpc-footprints/1 - Crops/Mushrooms.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10404"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10419"/>
   <workbookPr filterPrivacy="1" updateLinks="never" codeName="ThisWorkbook"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08F9DB2E-CC3F-654E-8FA3-0A0F6F3A77C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1BD64D9-6F1C-2C4D-92A1-90062CD1959E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29040" windowHeight="17640" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29040" windowHeight="17640" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="117" r:id="rId1"/>
@@ -1884,7 +1884,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="37" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="264">
+  <cellXfs count="266">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2563,6 +2563,10 @@
     </xf>
     <xf numFmtId="49" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="8" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="0" xfId="4" applyFill="1"/>
   </cellXfs>
   <cellStyles count="12">
     <cellStyle name="Hyperlink" xfId="11" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -3662,8 +3666,8 @@
         <v>289</v>
       </c>
     </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A11" s="150" t="s">
+    <row r="11" spans="1:22" s="265" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="264" t="s">
         <v>290</v>
       </c>
     </row>
@@ -31288,12 +31292,11 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="20b5f8f8-e964-4ea5-9bc5-5fa83731a92f" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -31532,17 +31535,20 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="20b5f8f8-e964-4ea5-9bc5-5fa83731a92f" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A16A6EDB-4C6A-433C-9B54-BF88B9AEEE87}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{627ED23C-5EEB-4F10-AA20-79B788D8342E}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="20b5f8f8-e964-4ea5-9bc5-5fa83731a92f"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -31567,11 +31573,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{627ED23C-5EEB-4F10-AA20-79B788D8342E}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A16A6EDB-4C6A-433C-9B54-BF88B9AEEE87}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="20b5f8f8-e964-4ea5-9bc5-5fa83731a92f"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>